--- a/EDE Models.xlsx
+++ b/EDE Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofstandrews907-my.sharepoint.com/personal/ljb38_st-andrews_ac_uk/Documents/Documents/GitHub/ExtinctionReview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3638" documentId="11_F25DC773A252ABDACC1048F9119F7EC45ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EF05DA4-24B3-446B-8EF5-CA882E7BDA1F}"/>
+  <xr:revisionPtr revIDLastSave="3642" documentId="11_F25DC773A252ABDACC1048F9119F7EC45ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D35E61-B63C-4D2D-B673-32B8DC54FD09}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -863,17 +863,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,10 +890,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1186,24 +1182,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="L1" s="11" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="L1" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11" t="s">
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1313,7 +1309,7 @@
       <c r="Q3" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1327,19 +1323,19 @@
       <c r="C4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="12">
         <v>1989</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="11" t="s">
         <v>60</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1369,7 +1365,7 @@
       <c r="Q4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1383,11 +1379,11 @@
       <c r="C5" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="2" t="s">
         <v>119</v>
       </c>
@@ -1429,19 +1425,19 @@
       <c r="C6" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="12">
         <v>1993</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -1471,7 +1467,7 @@
       <c r="Q6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="R6" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1485,11 +1481,11 @@
       <c r="C7" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
       <c r="I7" s="2" t="s">
         <v>119</v>
       </c>
@@ -1573,7 +1569,7 @@
       <c r="Q8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="R8" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1629,7 +1625,7 @@
       <c r="Q9" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R9" s="12" t="s">
+      <c r="R9" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1643,19 +1639,19 @@
       <c r="C10" t="s">
         <v>174</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="12">
         <v>1995</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1685,7 +1681,7 @@
       <c r="Q10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R10" s="12" t="s">
+      <c r="R10" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1699,11 +1695,11 @@
       <c r="C11" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="2" t="s">
         <v>119</v>
       </c>
@@ -1731,7 +1727,7 @@
       <c r="Q11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R11" s="12" t="s">
+      <c r="R11" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1745,11 +1741,11 @@
       <c r="C12" t="s">
         <v>176</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
       <c r="I12" s="2" t="s">
         <v>119</v>
       </c>
@@ -1777,7 +1773,7 @@
       <c r="Q12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R12" s="12" t="s">
+      <c r="R12" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1833,7 +1829,7 @@
       <c r="Q13" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R13" s="12" t="s">
+      <c r="R13" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1889,7 +1885,7 @@
       <c r="Q14" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R14" s="12" t="s">
+      <c r="R14" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1945,7 +1941,7 @@
       <c r="Q15" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R15" s="12" t="s">
+      <c r="R15" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2057,7 +2053,7 @@
       <c r="Q17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R17" s="12" t="s">
+      <c r="R17" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2113,7 +2109,7 @@
       <c r="Q18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R18" s="12" t="s">
+      <c r="R18" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2169,7 +2165,7 @@
       <c r="Q19" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R19" s="12" t="s">
+      <c r="R19" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2239,19 +2235,19 @@
       <c r="C21" t="s">
         <v>181</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="12">
         <v>2010</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="11" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2281,7 +2277,7 @@
       <c r="Q21" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R21" s="12" t="s">
+      <c r="R21" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2295,11 +2291,11 @@
       <c r="C22" t="s">
         <v>182</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="2" t="s">
         <v>119</v>
       </c>
@@ -2327,7 +2323,7 @@
       <c r="Q22" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R22" s="12" t="s">
+      <c r="R22" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2383,7 +2379,7 @@
       <c r="Q23" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R23" s="12" t="s">
+      <c r="R23" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2453,19 +2449,19 @@
       <c r="C25" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="12">
         <v>2013</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="11" t="s">
         <v>46</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -2509,11 +2505,11 @@
       <c r="C26" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
       <c r="I26" s="2" t="s">
         <v>119</v>
       </c>
@@ -2555,11 +2551,11 @@
       <c r="C27" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
       <c r="I27" s="2" t="s">
         <v>119</v>
       </c>
@@ -2601,19 +2597,19 @@
       <c r="C28" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="12">
         <v>2014</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="11" t="s">
         <v>69</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -2657,11 +2653,11 @@
       <c r="C29" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
       <c r="I29" s="2" t="s">
         <v>163</v>
       </c>
@@ -2703,19 +2699,19 @@
       <c r="C30" t="s">
         <v>189</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="12">
         <v>2014</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="11" t="s">
         <v>57</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2759,11 +2755,11 @@
       <c r="C31" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
       <c r="I31" s="2" t="s">
         <v>119</v>
       </c>
@@ -2847,7 +2843,7 @@
       <c r="Q32" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R32" s="12" t="s">
+      <c r="R32" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2973,19 +2969,19 @@
       <c r="C35" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="12">
         <v>2014</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="11" t="s">
         <v>53</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -3029,11 +3025,11 @@
       <c r="C36" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
       <c r="I36" s="2" t="s">
         <v>119</v>
       </c>
@@ -3131,19 +3127,19 @@
       <c r="C38" t="s">
         <v>186</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="12">
         <v>2016</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="11" t="s">
         <v>89</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -3187,11 +3183,11 @@
       <c r="C39" t="s">
         <v>187</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
       <c r="I39" s="2" t="s">
         <v>119</v>
       </c>
@@ -3331,7 +3327,7 @@
       <c r="Q41" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R41" s="12" t="s">
+      <c r="R41" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3345,19 +3341,19 @@
       <c r="C42" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="12">
         <v>2019</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="11" t="s">
         <v>74</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -3387,7 +3383,7 @@
       <c r="Q42" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R42" s="12" t="s">
+      <c r="R42" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3401,11 +3397,11 @@
       <c r="C43" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
       <c r="I43" s="2" t="s">
         <v>119</v>
       </c>
@@ -3433,7 +3429,7 @@
       <c r="Q43" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R43" s="12" t="s">
+      <c r="R43" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3447,11 +3443,11 @@
       <c r="C44" t="s">
         <v>33</v>
       </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
       <c r="I44" s="2" t="s">
         <v>119</v>
       </c>
@@ -3479,7 +3475,7 @@
       <c r="Q44" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R44" s="12" t="s">
+      <c r="R44" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3493,11 +3489,11 @@
       <c r="C45" t="s">
         <v>203</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
       <c r="I45" s="2" t="s">
         <v>119</v>
       </c>
@@ -3525,7 +3521,7 @@
       <c r="Q45" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R45" s="12" t="s">
+      <c r="R45" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3539,11 +3535,11 @@
       <c r="C46" t="s">
         <v>204</v>
       </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
       <c r="I46" s="2" t="s">
         <v>119</v>
       </c>
@@ -3571,7 +3567,7 @@
       <c r="Q46" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R46" s="12" t="s">
+      <c r="R46" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3641,19 +3637,19 @@
       <c r="C48" t="s">
         <v>196</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="12">
         <v>2020</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="11" t="s">
         <v>82</v>
       </c>
       <c r="I48" s="2" t="s">
@@ -3697,11 +3693,11 @@
       <c r="C49" t="s">
         <v>184</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
       <c r="I49" s="2" t="s">
         <v>119</v>
       </c>
@@ -3806,6 +3802,48 @@
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="F42:F46"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="G48:G49"/>
@@ -3822,48 +3860,6 @@
     <mergeCell ref="H35:H36"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="G25:G27"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="E42:E46"/>
-    <mergeCell ref="F42:F46"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="F28:F29"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions gridLines="1"/>

--- a/EDE Models.xlsx
+++ b/EDE Models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofstandrews907-my.sharepoint.com/personal/ljb38_st-andrews_ac_uk/Documents/Documents/GitHub/ExtinctionReview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3642" documentId="11_F25DC773A252ABDACC1048F9119F7EC45ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D35E61-B63C-4D2D-B673-32B8DC54FD09}"/>
+  <xr:revisionPtr revIDLastSave="3645" documentId="11_F25DC773A252ABDACC1048F9119F7EC45ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04EC5B3D-A6C3-4F28-8229-F8DFCFBDED98}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="245">
   <si>
     <t>Year</t>
   </si>
@@ -689,18 +689,6 @@
     <t>Outputs</t>
   </si>
   <si>
-    <t>Est.</t>
-  </si>
-  <si>
-    <t>Int.</t>
-  </si>
-  <si>
-    <t>Prob.</t>
-  </si>
-  <si>
-    <t>B. Fact.</t>
-  </si>
-  <si>
     <t>Inputs</t>
   </si>
   <si>
@@ -741,13 +729,58 @@
   </si>
   <si>
     <t>dodo?</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>Bayes Factor</t>
+  </si>
+  <si>
+    <t>Which Used</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Confidence</t>
+  </si>
+  <si>
+    <t>Conf. Int.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Credible</t>
+  </si>
+  <si>
+    <t>Cred. Int.</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>P(Extinct)</t>
+  </si>
+  <si>
+    <t>Bayes Fact.</t>
+  </si>
+  <si>
+    <t>Proxy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -804,14 +837,6 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -835,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -863,17 +888,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1158,7 +1180,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -1175,35 +1197,37 @@
     <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D1" s="10" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="L1" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="L1" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>125</v>
@@ -1227,10 +1251,10 @@
         <v>4</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>206</v>
@@ -1242,22 +1266,25 @@
         <v>7</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1286,7 +1313,7 @@
         <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K3" t="s">
         <v>207</v>
@@ -1295,25 +1322,28 @@
         <v>209</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O3" t="s">
+        <v>235</v>
+      </c>
+      <c r="P3" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1323,26 +1353,26 @@
       <c r="C4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="9">
         <v>1989</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>60</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K4" t="s">
         <v>207</v>
@@ -1351,25 +1381,28 @@
         <v>209</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O4" t="s">
+        <v>238</v>
+      </c>
+      <c r="P4" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1379,16 +1412,16 @@
       <c r="C5" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K5" t="s">
         <v>105</v>
@@ -1397,25 +1430,28 @@
         <v>209</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O5" t="s">
+        <v>238</v>
+      </c>
+      <c r="P5" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R5" t="s">
+        <v>235</v>
+      </c>
+      <c r="S5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1425,19 +1461,19 @@
       <c r="C6" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>1993</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -1453,25 +1489,29 @@
         <v>209</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P6" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>241</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" ref="S6:S8" si="0">Q6</f>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1481,11 +1521,11 @@
       <c r="C7" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="2" t="s">
         <v>119</v>
       </c>
@@ -1499,25 +1539,29 @@
         <v>209</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>242</v>
+      </c>
+      <c r="R7" t="s">
+        <v>238</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="0"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1555,25 +1599,29 @@
         <v>209</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O8" t="s">
+        <v>238</v>
+      </c>
+      <c r="P8" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>241</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="0"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1602,7 +1650,7 @@
         <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K9" t="s">
         <v>207</v>
@@ -1611,25 +1659,28 @@
         <v>209</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1639,19 +1690,19 @@
       <c r="C10" t="s">
         <v>174</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>1995</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1667,25 +1718,29 @@
         <v>210</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>241</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" ref="S10:S12" si="1">Q10</f>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1695,11 +1750,11 @@
       <c r="C11" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="2" t="s">
         <v>119</v>
       </c>
@@ -1713,25 +1768,29 @@
         <v>210</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>241</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="1"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1741,11 +1800,11 @@
       <c r="C12" t="s">
         <v>176</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="2" t="s">
         <v>119</v>
       </c>
@@ -1759,25 +1818,29 @@
         <v>210</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>241</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="1"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1806,7 +1869,7 @@
         <v>119</v>
       </c>
       <c r="J13" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K13" t="s">
         <v>207</v>
@@ -1815,25 +1878,28 @@
         <v>210</v>
       </c>
       <c r="M13" t="s">
-        <v>7</v>
+        <v>244</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P13" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1871,25 +1937,29 @@
         <v>210</v>
       </c>
       <c r="M14" t="s">
-        <v>7</v>
+        <v>244</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>241</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" ref="S14:S22" si="2">Q14</f>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1918,7 +1988,7 @@
         <v>119</v>
       </c>
       <c r="J15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K15" t="s">
         <v>207</v>
@@ -1927,25 +1997,29 @@
         <v>209</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P15" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>241</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="2"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1974,7 +2048,7 @@
         <v>119</v>
       </c>
       <c r="J16" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K16" t="s">
         <v>105</v>
@@ -1983,25 +2057,29 @@
         <v>211</v>
       </c>
       <c r="M16" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O16" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>242</v>
+      </c>
+      <c r="R16" t="s">
+        <v>235</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="2"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2039,25 +2117,29 @@
         <v>209</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O17" t="s">
+        <v>238</v>
+      </c>
+      <c r="P17" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>241</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="2"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2095,25 +2177,29 @@
         <v>209</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O18" t="s">
+        <v>238</v>
+      </c>
+      <c r="P18" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>241</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="2"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2151,25 +2237,29 @@
         <v>211</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P19" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>241</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="2"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2207,25 +2297,29 @@
         <v>211</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>242</v>
+      </c>
+      <c r="R20" t="s">
+        <v>238</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="2"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2235,19 +2329,19 @@
       <c r="C21" t="s">
         <v>181</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="9">
         <v>2010</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2263,25 +2357,29 @@
         <v>209</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P21" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>241</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S21" t="str">
+        <f t="shared" si="2"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2291,11 +2389,11 @@
       <c r="C22" t="s">
         <v>182</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="2" t="s">
         <v>119</v>
       </c>
@@ -2309,25 +2407,29 @@
         <v>209</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P22" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>241</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="2"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2356,7 +2458,7 @@
         <v>119</v>
       </c>
       <c r="J23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K23" t="s">
         <v>207</v>
@@ -2365,25 +2467,28 @@
         <v>209</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O23" t="s">
+        <v>238</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2421,25 +2526,28 @@
         <v>212</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s">
-        <v>224</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R24" t="s">
+        <v>238</v>
+      </c>
+      <c r="S24" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2449,19 +2557,19 @@
       <c r="C25" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="9">
         <v>2013</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -2474,28 +2582,32 @@
         <v>105</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N25" t="s">
-        <v>225</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>242</v>
+      </c>
+      <c r="R25" t="s">
+        <v>235</v>
+      </c>
+      <c r="S25" t="str">
+        <f t="shared" ref="S25:S28" si="3">Q25</f>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2505,11 +2617,11 @@
       <c r="C26" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
       <c r="I26" s="2" t="s">
         <v>119</v>
       </c>
@@ -2520,28 +2632,32 @@
         <v>105</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N26" t="s">
-        <v>225</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>242</v>
+      </c>
+      <c r="R26" t="s">
+        <v>235</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="3"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2551,11 +2667,11 @@
       <c r="C27" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
       <c r="I27" s="2" t="s">
         <v>119</v>
       </c>
@@ -2566,28 +2682,32 @@
         <v>105</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N27" t="s">
-        <v>225</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>242</v>
+      </c>
+      <c r="R27" t="s">
+        <v>235</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="3"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2597,26 +2717,26 @@
       <c r="C28" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="9">
         <v>2014</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="10" t="s">
         <v>69</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K28" t="s">
         <v>105</v>
@@ -2625,25 +2745,29 @@
         <v>211</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>242</v>
+      </c>
+      <c r="R28" t="s">
+        <v>235</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="3"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2653,16 +2777,16 @@
       <c r="C29" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
       <c r="I29" s="2" t="s">
         <v>163</v>
       </c>
       <c r="J29" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K29" t="s">
         <v>105</v>
@@ -2671,25 +2795,28 @@
         <v>211</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R29" t="s">
+        <v>235</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2699,19 +2826,19 @@
       <c r="C30" t="s">
         <v>189</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="9">
         <v>2014</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="10" t="s">
         <v>57</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2727,25 +2854,29 @@
         <v>211</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O30" t="s">
+        <v>238</v>
+      </c>
+      <c r="P30" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>242</v>
+      </c>
+      <c r="R30" t="s">
+        <v>235</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" ref="S30:S34" si="4">Q30</f>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2755,11 +2886,11 @@
       <c r="C31" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
       <c r="I31" s="2" t="s">
         <v>119</v>
       </c>
@@ -2773,25 +2904,29 @@
         <v>211</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O31" t="s">
+        <v>238</v>
+      </c>
+      <c r="P31" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>242</v>
+      </c>
+      <c r="R31" t="s">
+        <v>235</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="4"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2829,25 +2964,29 @@
         <v>213</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N32" t="s">
-        <v>226</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R32" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="O32" t="s">
+        <v>238</v>
+      </c>
+      <c r="P32" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>241</v>
+      </c>
+      <c r="R32" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="4"/>
+        <v>P-value</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2885,25 +3024,29 @@
         <v>214</v>
       </c>
       <c r="M33" t="s">
+        <v>218</v>
+      </c>
+      <c r="N33" t="s">
         <v>222</v>
       </c>
-      <c r="N33" t="s">
-        <v>226</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O33" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>242</v>
+      </c>
+      <c r="R33" t="s">
+        <v>235</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="4"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2941,25 +3084,29 @@
         <v>212</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N34" t="s">
-        <v>224</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="O34" t="s">
+        <v>238</v>
+      </c>
+      <c r="P34" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>242</v>
+      </c>
+      <c r="R34" t="s">
+        <v>235</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="4"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2969,19 +3116,19 @@
       <c r="C35" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="9">
         <v>2014</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="10" t="s">
         <v>53</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -2997,25 +3144,28 @@
         <v>212</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N35" t="s">
-        <v>224</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R35" t="s">
+        <v>238</v>
+      </c>
+      <c r="S35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3025,11 +3175,11 @@
       <c r="C36" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
       <c r="I36" s="2" t="s">
         <v>119</v>
       </c>
@@ -3043,25 +3193,28 @@
         <v>212</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N36" t="s">
-        <v>224</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R36" t="s">
+        <v>238</v>
+      </c>
+      <c r="S36" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3099,25 +3252,29 @@
         <v>211</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N37" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>242</v>
+      </c>
+      <c r="R37" t="s">
+        <v>235</v>
+      </c>
+      <c r="S37" t="str">
+        <f t="shared" ref="S37:S39" si="5">Q37</f>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3127,26 +3284,26 @@
       <c r="C38" t="s">
         <v>186</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="9">
         <v>2016</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="10" t="s">
         <v>89</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J38" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K38" t="s">
         <v>105</v>
@@ -3155,25 +3312,29 @@
         <v>211</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>242</v>
+      </c>
+      <c r="R38" t="s">
+        <v>235</v>
+      </c>
+      <c r="S38" t="str">
+        <f t="shared" si="5"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3183,16 +3344,16 @@
       <c r="C39" t="s">
         <v>187</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
       <c r="I39" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J39" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K39" t="s">
         <v>105</v>
@@ -3201,25 +3362,29 @@
         <v>211</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>242</v>
+      </c>
+      <c r="R39" t="s">
+        <v>235</v>
+      </c>
+      <c r="S39" t="str">
+        <f t="shared" si="5"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3248,7 +3413,7 @@
         <v>119</v>
       </c>
       <c r="J40" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K40" t="s">
         <v>105</v>
@@ -3257,25 +3422,28 @@
         <v>209</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N40" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O40" t="s">
+        <v>238</v>
+      </c>
+      <c r="P40" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R40" t="s">
+        <v>235</v>
+      </c>
+      <c r="S40" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3313,25 +3481,29 @@
         <v>214</v>
       </c>
       <c r="M41" t="s">
+        <v>218</v>
+      </c>
+      <c r="N41" t="s">
         <v>222</v>
       </c>
-      <c r="N41" t="s">
-        <v>226</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R41" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O41" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>242</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S41" t="str">
+        <f t="shared" ref="S41:S49" si="6">Q41</f>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3341,19 +3513,19 @@
       <c r="C42" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="9">
         <v>2019</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="10" t="s">
         <v>74</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -3369,25 +3541,29 @@
         <v>213</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N42" t="s">
-        <v>226</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R42" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="O42" t="s">
+        <v>238</v>
+      </c>
+      <c r="P42" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>242</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S42" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3397,11 +3573,11 @@
       <c r="C43" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
       <c r="I43" s="2" t="s">
         <v>119</v>
       </c>
@@ -3415,25 +3591,29 @@
         <v>213</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N43" t="s">
-        <v>226</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R43" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="O43" t="s">
+        <v>238</v>
+      </c>
+      <c r="P43" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>242</v>
+      </c>
+      <c r="R43" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S43" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3443,11 +3623,11 @@
       <c r="C44" t="s">
         <v>33</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
       <c r="I44" s="2" t="s">
         <v>119</v>
       </c>
@@ -3461,25 +3641,29 @@
         <v>213</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N44" t="s">
-        <v>226</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R44" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="O44" t="s">
+        <v>238</v>
+      </c>
+      <c r="P44" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>242</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S44" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3489,11 +3673,11 @@
       <c r="C45" t="s">
         <v>203</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
       <c r="I45" s="2" t="s">
         <v>119</v>
       </c>
@@ -3507,25 +3691,29 @@
         <v>213</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N45" t="s">
-        <v>226</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R45" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="O45" t="s">
+        <v>238</v>
+      </c>
+      <c r="P45" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>242</v>
+      </c>
+      <c r="R45" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S45" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3535,11 +3723,11 @@
       <c r="C46" t="s">
         <v>204</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
       <c r="I46" s="2" t="s">
         <v>119</v>
       </c>
@@ -3553,25 +3741,29 @@
         <v>213</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N46" t="s">
-        <v>226</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R46" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="O46" t="s">
+        <v>238</v>
+      </c>
+      <c r="P46" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>242</v>
+      </c>
+      <c r="R46" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="S46" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3609,25 +3801,29 @@
         <v>214</v>
       </c>
       <c r="M47" t="s">
+        <v>218</v>
+      </c>
+      <c r="N47" t="s">
         <v>222</v>
       </c>
-      <c r="N47" t="s">
-        <v>226</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O47" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="P47" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>242</v>
+      </c>
+      <c r="R47" t="s">
+        <v>238</v>
+      </c>
+      <c r="S47" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3637,19 +3833,19 @@
       <c r="C48" t="s">
         <v>196</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="9">
         <v>2020</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="10" t="s">
         <v>82</v>
       </c>
       <c r="I48" s="2" t="s">
@@ -3665,25 +3861,29 @@
         <v>211</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O48" t="s">
+        <v>238</v>
+      </c>
+      <c r="P48" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>242</v>
+      </c>
+      <c r="R48" t="s">
+        <v>235</v>
+      </c>
+      <c r="S48" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3693,11 +3893,11 @@
       <c r="C49" t="s">
         <v>184</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
       <c r="I49" s="2" t="s">
         <v>119</v>
       </c>
@@ -3711,25 +3911,29 @@
         <v>212</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N49" t="s">
-        <v>224</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="O49" t="s">
+        <v>238</v>
+      </c>
+      <c r="P49" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>242</v>
+      </c>
+      <c r="R49" t="s">
+        <v>235</v>
+      </c>
+      <c r="S49" t="str">
+        <f t="shared" si="6"/>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3767,54 +3971,74 @@
         <v>212</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N50" t="s">
-        <v>224</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="O50" t="s">
+        <v>238</v>
+      </c>
+      <c r="P50" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>242</v>
+      </c>
+      <c r="R50" t="s">
+        <v>235</v>
+      </c>
+      <c r="S50" t="str">
+        <f>Q50</f>
+        <v>P(Extinct)</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H52" s="3"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H53" s="3"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H54" s="3"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G42:G46"/>
+    <mergeCell ref="H42:H46"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="F42:F46"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
@@ -3831,35 +4055,19 @@
     <mergeCell ref="F10:F12"/>
     <mergeCell ref="G10:G12"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="E42:E46"/>
-    <mergeCell ref="F42:F46"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G42:G46"/>
-    <mergeCell ref="H42:H46"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions gridLines="1"/>
